--- a/pipeline/credit_rating/output/fiinratings_xhtn_20261005.xlsx
+++ b/pipeline/credit_rating/output/fiinratings_xhtn_20261005.xlsx
@@ -557,7 +557,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O2" s="1" t="n">
@@ -628,7 +628,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O3" s="1" t="n">
@@ -699,7 +699,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O4" s="1" t="n">
@@ -762,7 +762,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O5" s="1" t="n">
@@ -833,7 +833,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O6" s="1" t="n">
@@ -908,7 +908,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O7" s="1" t="n">
@@ -975,7 +975,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O8" s="1" t="n">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O9" s="1" t="n">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O10" s="1" t="n">
@@ -1154,7 +1154,11 @@
           <t>https://cms.fiinratings.vn//UploadFile/15-07-2026/VN_FiinRatings_VIB_Issuer_Surv04_2026_07_signed.pdf</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>https://cms.fiinratings.vn//UploadFile/15-07-2026/EN_FiinRatings_VIB_Issuer_Surv04_2026_07_Print.pdf</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>https://fiinratings.vn/vi/ratings-fr/ngan-hang-thuong-aại-co-phan-qaoc-te-viet-naa-id4062.html</t>
@@ -1172,7 +1176,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O11" s="1" t="n">
@@ -1239,7 +1243,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O12" s="1" t="n">
@@ -1302,7 +1306,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O13" s="1" t="n">
@@ -1377,7 +1381,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O14" s="1" t="n">
@@ -1452,7 +1456,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O15" s="1" t="n">
@@ -1515,7 +1519,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O16" s="1" t="n">
@@ -1578,7 +1582,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O17" s="1" t="n">
@@ -1645,7 +1649,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O18" s="1" t="n">
@@ -1716,7 +1720,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O19" s="1" t="n">
@@ -1787,7 +1791,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O20" s="1" t="n">
@@ -1854,7 +1858,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O21" s="1" t="n">
@@ -1917,7 +1921,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O22" s="1" t="n">
@@ -1980,7 +1984,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O23" s="1" t="n">
@@ -2047,7 +2051,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O24" s="1" t="n">
@@ -2114,7 +2118,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O25" s="1" t="n">
@@ -2177,7 +2181,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O26" s="1" t="n">
@@ -2244,7 +2248,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O27" s="1" t="n">
@@ -2307,7 +2311,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O28" s="1" t="n">
@@ -2370,7 +2374,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O29" s="1" t="n">
@@ -2437,7 +2441,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O30" s="1" t="n">
@@ -2504,7 +2508,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O31" s="1" t="n">
@@ -2567,7 +2571,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O32" s="1" t="n">
@@ -2630,7 +2634,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O33" s="1" t="n">
@@ -2693,7 +2697,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O34" s="1" t="n">
@@ -2760,7 +2764,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O35" s="1" t="n">
@@ -2823,7 +2827,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O36" s="1" t="n">
@@ -2890,7 +2894,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O37" s="1" t="n">
@@ -2953,7 +2957,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O38" s="1" t="n">
@@ -3016,7 +3020,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O39" s="1" t="n">
@@ -3079,7 +3083,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O40" s="1" t="n">
@@ -3146,7 +3150,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O41" s="1" t="n">
@@ -3213,7 +3217,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O42" s="1" t="n">
@@ -3276,7 +3280,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O43" s="1" t="n">
@@ -3339,7 +3343,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O44" s="1" t="n">
@@ -3402,7 +3406,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O45" s="1" t="n">
@@ -3469,7 +3473,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O46" s="1" t="n">
@@ -3532,7 +3536,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O47" s="1" t="n">
@@ -3595,7 +3599,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O48" s="1" t="n">
@@ -3658,7 +3662,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O49" s="1" t="n">
@@ -3721,7 +3725,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O50" s="1" t="n">
@@ -3784,7 +3788,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O51" s="1" t="n">
@@ -3847,7 +3851,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O52" s="1" t="n">
@@ -3910,7 +3914,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O53" s="1" t="n">
@@ -3977,7 +3981,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O54" s="1" t="n">
@@ -4040,7 +4044,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O55" s="1" t="n">
@@ -4107,7 +4111,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O56" s="1" t="n">
@@ -4170,7 +4174,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O57" s="1" t="n">
@@ -4233,7 +4237,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O58" s="1" t="n">
@@ -4296,7 +4300,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O59" s="1" t="n">
@@ -4359,7 +4363,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O60" s="1" t="n">
@@ -4422,7 +4426,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O61" s="1" t="n">
@@ -4485,7 +4489,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O62" s="1" t="n">
@@ -4548,7 +4552,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O63" s="1" t="n">
@@ -4611,7 +4615,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O64" s="1" t="n">
@@ -4678,7 +4682,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O65" s="1" t="n">
@@ -4741,7 +4745,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O66" s="1" t="n">
@@ -4804,7 +4808,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O67" s="1" t="n">
@@ -4871,7 +4875,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O68" s="1" t="n">
@@ -4934,7 +4938,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O69" s="1" t="n">
@@ -5001,7 +5005,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O70" s="1" t="n">
@@ -5064,7 +5068,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O71" s="1" t="n">
@@ -5127,7 +5131,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O72" s="1" t="n">
@@ -5190,7 +5194,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O73" s="1" t="n">
@@ -5253,7 +5257,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O74" s="1" t="n">
@@ -5316,7 +5320,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O75" s="1" t="n">
@@ -5383,7 +5387,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O76" s="1" t="n">
@@ -5446,7 +5450,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O77" s="1" t="n">
@@ -5509,7 +5513,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O78" s="1" t="n">
@@ -5572,7 +5576,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O79" s="1" t="n">
@@ -5635,7 +5639,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O80" s="1" t="n">
@@ -5698,7 +5702,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O81" s="1" t="n">
@@ -5761,7 +5765,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O82" s="1" t="n">
@@ -5828,7 +5832,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O83" s="1" t="n">
@@ -5891,7 +5895,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O84" s="1" t="n">
@@ -5954,7 +5958,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O85" s="1" t="n">
@@ -6017,7 +6021,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O86" s="1" t="n">
@@ -6080,7 +6084,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O87" s="1" t="n">
@@ -6143,7 +6147,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O88" s="1" t="n">
@@ -6206,7 +6210,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O89" s="1" t="n">
@@ -6269,7 +6273,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O90" s="1" t="n">
@@ -6332,7 +6336,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O91" s="1" t="n">
@@ -6395,7 +6399,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O92" s="1" t="n">
@@ -6458,7 +6462,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O93" s="1" t="n">
@@ -6521,7 +6525,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O94" s="1" t="n">
@@ -6584,7 +6588,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O95" s="1" t="n">
@@ -6647,7 +6651,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O96" s="1" t="n">
@@ -6710,7 +6714,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O97" s="1" t="n">
@@ -6777,7 +6781,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O98" s="1" t="n">
@@ -6840,7 +6844,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O99" s="1" t="n">
@@ -6903,7 +6907,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O100" s="1" t="n">
@@ -6970,7 +6974,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O101" s="1" t="n">
@@ -7033,7 +7037,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O102" s="1" t="n">
@@ -7096,7 +7100,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O103" s="1" t="n">
@@ -7159,7 +7163,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O104" s="1" t="n">
@@ -7226,7 +7230,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O105" s="1" t="n">
@@ -7289,7 +7293,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O106" s="1" t="n">
@@ -7352,7 +7356,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O107" s="1" t="n">
@@ -7415,7 +7419,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O108" s="1" t="n">
@@ -7478,7 +7482,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O109" s="1" t="n">
@@ -7541,7 +7545,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O110" s="1" t="n">
@@ -7604,7 +7608,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O111" s="1" t="n">
@@ -7671,7 +7675,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O112" s="1" t="n">
@@ -7734,7 +7738,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O113" s="1" t="n">
@@ -7797,7 +7801,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O114" s="1" t="n">
@@ -7860,7 +7864,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O115" s="1" t="n">
@@ -7923,7 +7927,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O116" s="1" t="n">
@@ -7986,7 +7990,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O117" s="1" t="n">
@@ -8049,7 +8053,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O118" s="1" t="n">
@@ -8112,7 +8116,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O119" s="1" t="n">
@@ -8175,7 +8179,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O120" s="1" t="n">
@@ -8238,7 +8242,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O121" s="1" t="n">
@@ -8301,7 +8305,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O122" s="1" t="n">
@@ -8364,7 +8368,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O123" s="1" t="n">
@@ -8427,7 +8431,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O124" s="1" t="n">
@@ -8490,7 +8494,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O125" s="1" t="n">
@@ -8553,7 +8557,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O126" s="1" t="n">
@@ -8616,7 +8620,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O127" s="1" t="n">
@@ -8679,7 +8683,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O128" s="1" t="n">
@@ -8742,7 +8746,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O129" s="1" t="n">
@@ -8805,7 +8809,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O130" s="1" t="n">
@@ -8872,7 +8876,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O131" s="1" t="n">
@@ -8935,7 +8939,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O132" s="1" t="n">
@@ -9002,7 +9006,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O133" s="1" t="n">
@@ -9065,7 +9069,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O134" s="1" t="n">
@@ -9128,7 +9132,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O135" s="1" t="n">
@@ -9191,7 +9195,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O136" s="1" t="n">
@@ -9258,7 +9262,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O137" s="1" t="n">
@@ -9321,7 +9325,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O138" s="1" t="n">
@@ -9384,7 +9388,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O139" s="1" t="n">
@@ -9447,7 +9451,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O140" s="1" t="n">
@@ -9510,7 +9514,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O141" s="1" t="n">
@@ -9573,7 +9577,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O142" s="1" t="n">
@@ -9636,7 +9640,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O143" s="1" t="n">
@@ -9699,7 +9703,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O144" s="1" t="n">
@@ -9762,7 +9766,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O145" s="1" t="n">
@@ -9825,7 +9829,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O146" s="1" t="n">
@@ -9888,7 +9892,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O147" s="1" t="n">
@@ -9951,7 +9955,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O148" s="1" t="n">
@@ -10014,7 +10018,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O149" s="1" t="n">
@@ -10077,7 +10081,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O150" s="1" t="n">
@@ -10140,7 +10144,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O151" s="1" t="n">
@@ -10203,7 +10207,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O152" s="1" t="n">
@@ -10266,7 +10270,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O153" s="1" t="n">
@@ -10329,7 +10333,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O154" s="1" t="n">
@@ -10392,7 +10396,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O155" s="1" t="n">
@@ -10455,7 +10459,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O156" s="1" t="n">
@@ -10518,7 +10522,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O157" s="1" t="n">
@@ -10581,7 +10585,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O158" s="1" t="n">
@@ -10644,7 +10648,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O159" s="1" t="n">
@@ -10707,7 +10711,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O160" s="1" t="n">
@@ -10770,7 +10774,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O161" s="1" t="n">
@@ -10833,7 +10837,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O162" s="1" t="n">
@@ -10896,7 +10900,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O163" s="1" t="n">
@@ -10959,7 +10963,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O164" s="1" t="n">
@@ -11022,7 +11026,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O165" s="1" t="n">
@@ -11085,7 +11089,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O166" s="1" t="n">
@@ -11148,7 +11152,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O167" s="1" t="n">
@@ -11211,7 +11215,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O168" s="1" t="n">
@@ -11274,7 +11278,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O169" s="1" t="n">
@@ -11337,7 +11341,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O170" s="1" t="n">
@@ -11400,7 +11404,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O171" s="1" t="n">
@@ -11463,7 +11467,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O172" s="1" t="n">
@@ -11526,7 +11530,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O173" s="1" t="n">
@@ -11589,7 +11593,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O174" s="1" t="n">
@@ -11652,7 +11656,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O175" s="1" t="n">
@@ -11715,7 +11719,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O176" s="1" t="n">
@@ -11778,7 +11782,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O177" s="1" t="n">
@@ -11841,7 +11845,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O178" s="1" t="n">
@@ -11904,7 +11908,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O179" s="1" t="n">
@@ -11967,7 +11971,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O180" s="1" t="n">
@@ -12030,7 +12034,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O181" s="1" t="n">
@@ -12093,7 +12097,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O182" s="1" t="n">
@@ -12156,7 +12160,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O183" s="1" t="n">
@@ -12219,7 +12223,7 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O184" s="1" t="n">
@@ -12282,7 +12286,7 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O185" s="1" t="n">
@@ -12345,7 +12349,7 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O186" s="1" t="n">
@@ -12408,7 +12412,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O187" s="1" t="n">
@@ -12471,7 +12475,7 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O188" s="1" t="n">
@@ -12534,7 +12538,7 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O189" s="1" t="n">
@@ -12597,7 +12601,7 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O190" s="1" t="n">
@@ -12660,7 +12664,7 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O191" s="1" t="n">
@@ -12723,7 +12727,7 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O192" s="1" t="n">
@@ -12786,7 +12790,7 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O193" s="1" t="n">
@@ -12849,7 +12853,7 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O194" s="1" t="n">
@@ -12912,7 +12916,7 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O195" s="1" t="n">
@@ -12975,7 +12979,7 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O196" s="1" t="n">
@@ -13038,7 +13042,7 @@
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O197" s="1" t="n">
@@ -13101,7 +13105,7 @@
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O198" s="1" t="n">
@@ -13164,7 +13168,7 @@
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>2026-10-05 10:48:11</t>
+          <t>2026-10-05 17:19:56</t>
         </is>
       </c>
       <c r="O199" s="1" t="n">
